--- a/docs/i18n_dictionary.xlsx
+++ b/docs/i18n_dictionary.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="332">
   <si>
     <t>Pantalla</t>
   </si>
@@ -61,96 +61,105 @@
     <t>en-US</t>
   </si>
   <si>
+    <t>Descripción de página</t>
+  </si>
+  <si>
+    <t>Debe ser claro</t>
+  </si>
+  <si>
+    <t>UsernameLbl</t>
+  </si>
+  <si>
+    <t>Player_Username</t>
+  </si>
+  <si>
+    <t>Nombre de usuario</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Descripción de campo</t>
+  </si>
+  <si>
+    <t>EmailLbl</t>
+  </si>
+  <si>
+    <t>Player_Email</t>
+  </si>
+  <si>
+    <t>Correo electrónico</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Debe referirse al correo electrónico</t>
+  </si>
+  <si>
+    <t>PasswordLbl</t>
+  </si>
+  <si>
+    <t>Player_Password</t>
+  </si>
+  <si>
+    <t>Contraseña</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>AccountQuestionLbl</t>
+  </si>
+  <si>
+    <t>SignupPage_AccountQuestion</t>
+  </si>
+  <si>
+    <t>¿Ya tienes una cuenta?</t>
+  </si>
+  <si>
+    <t>Do you have an account?</t>
+  </si>
+  <si>
+    <t>Cambio de página</t>
+  </si>
+  <si>
+    <t>Debe ser corto</t>
+  </si>
+  <si>
+    <t>LoginLink</t>
+  </si>
+  <si>
+    <t>HyperLink</t>
+  </si>
+  <si>
+    <t>SignupPage_LoginLink</t>
+  </si>
+  <si>
+    <t>Iniciar Sesión</t>
+  </si>
+  <si>
+    <t>Log In</t>
+  </si>
+  <si>
+    <t>RegisterBtn</t>
+  </si>
+  <si>
+    <t>Button</t>
+  </si>
+  <si>
+    <t>SignupPage_Register</t>
+  </si>
+  <si>
+    <t>Registrar</t>
+  </si>
+  <si>
+    <t>Register</t>
+  </si>
+  <si>
     <t>Registro de cuenta</t>
   </si>
   <si>
-    <t>Debe ser claro</t>
-  </si>
-  <si>
-    <t>UsernameLbl</t>
-  </si>
-  <si>
-    <t>Player_Username</t>
-  </si>
-  <si>
-    <t>Nombre de usuario</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>EmailLbl</t>
-  </si>
-  <si>
-    <t>Player_Email</t>
-  </si>
-  <si>
-    <t>Correo electrónico</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Debe referirse al correo electrónico</t>
-  </si>
-  <si>
-    <t>PasswordLbl</t>
-  </si>
-  <si>
-    <t>Player_Password</t>
-  </si>
-  <si>
-    <t>Contraseña</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>AccountQuestionLbl</t>
-  </si>
-  <si>
-    <t>SignupPage_AccountQuestion</t>
-  </si>
-  <si>
-    <t>¿Ya tienes una cuenta?</t>
-  </si>
-  <si>
-    <t>Do you have an account?</t>
-  </si>
-  <si>
-    <t>Cambio de página</t>
-  </si>
-  <si>
-    <t>Debe ser corto</t>
-  </si>
-  <si>
-    <t>LoginLink</t>
-  </si>
-  <si>
-    <t>SignupPage_LoginLink</t>
-  </si>
-  <si>
-    <t>Iniciar Sesión</t>
-  </si>
-  <si>
-    <t>Log In</t>
-  </si>
-  <si>
-    <t>RegisterBtn</t>
-  </si>
-  <si>
-    <t>Button</t>
-  </si>
-  <si>
-    <t>SignupPage_Register</t>
-  </si>
-  <si>
-    <t>Registrar</t>
-  </si>
-  <si>
-    <t>Register</t>
-  </si>
-  <si>
     <t>LoginPage</t>
   </si>
   <si>
@@ -182,13 +191,829 @@
   </si>
   <si>
     <t>LoginPage_Login</t>
+  </si>
+  <si>
+    <t>MainPage</t>
+  </si>
+  <si>
+    <t>MainPage_Title</t>
+  </si>
+  <si>
+    <t>¡Vamos a Descifrar!</t>
+  </si>
+  <si>
+    <t>Let's Decipher!</t>
+  </si>
+  <si>
+    <t>PlayBtn</t>
+  </si>
+  <si>
+    <t>MainPage_Play</t>
+  </si>
+  <si>
+    <t>Jugar</t>
+  </si>
+  <si>
+    <t>Play</t>
+  </si>
+  <si>
+    <t>Página Principal</t>
+  </si>
+  <si>
+    <t>ProfileBtn</t>
+  </si>
+  <si>
+    <t>MainPage_Profile</t>
+  </si>
+  <si>
+    <t>Perfil</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>FriendsBtn</t>
+  </si>
+  <si>
+    <t>MainPage_Friends</t>
+  </si>
+  <si>
+    <t>Amigos</t>
+  </si>
+  <si>
+    <t>Friends</t>
+  </si>
+  <si>
+    <t>QuitBtn</t>
+  </si>
+  <si>
+    <t>MainPage_Quit</t>
+  </si>
+  <si>
+    <t>Salir</t>
+  </si>
+  <si>
+    <t>Quit</t>
+  </si>
+  <si>
+    <t>RoomsPage</t>
+  </si>
+  <si>
+    <t>BackBtn</t>
+  </si>
+  <si>
+    <t>UI_Back</t>
+  </si>
+  <si>
+    <t>Regresar</t>
+  </si>
+  <si>
+    <t>Back</t>
+  </si>
+  <si>
+    <t>RoomsPage_Title</t>
+  </si>
+  <si>
+    <t>Salas de deciframiento</t>
+  </si>
+  <si>
+    <t>Deciphering Rooms</t>
+  </si>
+  <si>
+    <t>Debe sonar interesante</t>
+  </si>
+  <si>
+    <t>RefreshBtn</t>
+  </si>
+  <si>
+    <t>RoomsPage_Refresh</t>
+  </si>
+  <si>
+    <t>Actualizar</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>Actualizar página</t>
+  </si>
+  <si>
+    <t>JoinBtn</t>
+  </si>
+  <si>
+    <t>Unirse</t>
+  </si>
+  <si>
+    <t>Join</t>
+  </si>
+  <si>
+    <t>Entrar a una sala</t>
+  </si>
+  <si>
+    <t>CodeBtn</t>
+  </si>
+  <si>
+    <t>RoomsPage_Code</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>CreateBtn</t>
+  </si>
+  <si>
+    <t>RoomsPage_Create</t>
+  </si>
+  <si>
+    <t>Crear</t>
+  </si>
+  <si>
+    <t>Create</t>
+  </si>
+  <si>
+    <t>Crear una sala</t>
+  </si>
+  <si>
+    <t>CreateRoomPage</t>
+  </si>
+  <si>
+    <t>CreateRoomPage_Title</t>
+  </si>
+  <si>
+    <t>Crear una Sala</t>
+  </si>
+  <si>
+    <t>Create a Room</t>
+  </si>
+  <si>
+    <t>Debe ser descriptivo</t>
+  </si>
+  <si>
+    <t>RoomNameLbl</t>
+  </si>
+  <si>
+    <t>CreateRoomPage_Name</t>
+  </si>
+  <si>
+    <t>Nombre de la Sala</t>
+  </si>
+  <si>
+    <t>Room Name</t>
+  </si>
+  <si>
+    <t>ModeLbl</t>
+  </si>
+  <si>
+    <t>CreateRoomPage_Mode</t>
+  </si>
+  <si>
+    <t>Modo de juego</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>TimeTrialBtn</t>
+  </si>
+  <si>
+    <t>Gamemode_TimeTrial</t>
+  </si>
+  <si>
+    <t>Contrarreloj</t>
+  </si>
+  <si>
+    <t>Time Trial</t>
+  </si>
+  <si>
+    <t>Descripción de modo de juego</t>
+  </si>
+  <si>
+    <t>Debe ser descriptivo y juguetón</t>
+  </si>
+  <si>
+    <t>TriesBtn</t>
+  </si>
+  <si>
+    <t>Gamemode_Tries</t>
+  </si>
+  <si>
+    <t>Intentos</t>
+  </si>
+  <si>
+    <t>Tries</t>
+  </si>
+  <si>
+    <t>DifficultyLbl</t>
+  </si>
+  <si>
+    <t>CreateRoomPage_Difficulty</t>
+  </si>
+  <si>
+    <t>Dificultad</t>
+  </si>
+  <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
+    <t>EasyBtn</t>
+  </si>
+  <si>
+    <t>GameDifficulty_Easy</t>
+  </si>
+  <si>
+    <t>Fácil</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>NormalBtn</t>
+  </si>
+  <si>
+    <t>GameDifficulty_Normal</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>HardBtn</t>
+  </si>
+  <si>
+    <t>GameDifficulty_Hard</t>
+  </si>
+  <si>
+    <t>Difícil</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t>EnigmaBtn</t>
+  </si>
+  <si>
+    <t>GameDifficulty_Enigma</t>
+  </si>
+  <si>
+    <t>Enigma</t>
+  </si>
+  <si>
+    <t>RoomPrivacyLbl</t>
+  </si>
+  <si>
+    <t>CreateRoomPage_Privacy</t>
+  </si>
+  <si>
+    <t>Privacidad de Sala</t>
+  </si>
+  <si>
+    <t>Room Privacy</t>
+  </si>
+  <si>
+    <t>PrivateBtn</t>
+  </si>
+  <si>
+    <t>RoomPrivacy_Private</t>
+  </si>
+  <si>
+    <t>Privada</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>PublicBtn</t>
+  </si>
+  <si>
+    <t>RoomPrivacy_Public</t>
+  </si>
+  <si>
+    <t>Pública</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>CancelBtn</t>
+  </si>
+  <si>
+    <t>UI_Cancel</t>
+  </si>
+  <si>
+    <t>Cancelar</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>Descripción de acción</t>
+  </si>
+  <si>
+    <t>UI_Create</t>
+  </si>
+  <si>
+    <t>ProfilePage</t>
+  </si>
+  <si>
+    <t>UpdateBtn</t>
+  </si>
+  <si>
+    <t>ProfilePage_Update</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>ChangePasswordLink</t>
+  </si>
+  <si>
+    <t>ProfilePage_ChangePassword</t>
+  </si>
+  <si>
+    <t>Cambiar Contraseña</t>
+  </si>
+  <si>
+    <t>Change Password</t>
+  </si>
+  <si>
+    <t>RecordsLbl</t>
+  </si>
+  <si>
+    <t>ProfilePage_Records</t>
+  </si>
+  <si>
+    <t>Records</t>
+  </si>
+  <si>
+    <t>Descripción de sección</t>
+  </si>
+  <si>
+    <t>Debe ser corto y claro</t>
+  </si>
+  <si>
+    <t>BestTimeLbl</t>
+  </si>
+  <si>
+    <t>ProfilePage_BestTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejor Tiempo: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best Time: </t>
+  </si>
+  <si>
+    <t>SecondsLbl</t>
+  </si>
+  <si>
+    <t>ProfilePage_Seconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> seg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> sec.</t>
+  </si>
+  <si>
+    <t>LeastTriesLbl</t>
+  </si>
+  <si>
+    <t>ProfilePage_LeastTries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menos Intentos: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Least Tries: </t>
+  </si>
+  <si>
+    <t>ReportPlayerTxt</t>
+  </si>
+  <si>
+    <t>TextBox (Ex. text)</t>
+  </si>
+  <si>
+    <t>ProfilePage_ReportPlayer</t>
+  </si>
+  <si>
+    <t>Reportar a un jugador</t>
+  </si>
+  <si>
+    <t>Report a player</t>
+  </si>
+  <si>
+    <t>Descripción de elemento</t>
+  </si>
+  <si>
+    <t>UpdateProfilePage</t>
+  </si>
+  <si>
+    <t>SaveBtn</t>
+  </si>
+  <si>
+    <t>UpdateProfilePage_Save</t>
+  </si>
+  <si>
+    <t>Guardar</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>VerificationCodeModal</t>
+  </si>
+  <si>
+    <t>ModalTitleLbl</t>
+  </si>
+  <si>
+    <t>VerificationCodeModal_Title</t>
+  </si>
+  <si>
+    <t>Escribe el código de verificación</t>
+  </si>
+  <si>
+    <t>Type your verification code</t>
+  </si>
+  <si>
+    <t>Instrucción</t>
+  </si>
+  <si>
+    <t>AcceptBtn</t>
+  </si>
+  <si>
+    <t>UI_Accept</t>
+  </si>
+  <si>
+    <t>Aceptar</t>
+  </si>
+  <si>
+    <t>Accept</t>
+  </si>
+  <si>
+    <t>ResendCodeLink</t>
+  </si>
+  <si>
+    <t>Hyperlink</t>
+  </si>
+  <si>
+    <t>VerificationCodeModal_ResendCode</t>
+  </si>
+  <si>
+    <t>Reenviar código de verificación</t>
+  </si>
+  <si>
+    <t>Resend verification code</t>
+  </si>
+  <si>
+    <t>PrivateRoomCodeModal</t>
+  </si>
+  <si>
+    <t>PrivateRoomCodeModal_Title</t>
+  </si>
+  <si>
+    <t>Escribe el Código de la Sala</t>
+  </si>
+  <si>
+    <t>Type the Room Code</t>
+  </si>
+  <si>
+    <t>PrivateRoomCodeModal_Join</t>
+  </si>
+  <si>
+    <t>EscapeBtn</t>
+  </si>
+  <si>
+    <t>PrivateRoomCodeModal_Escape</t>
+  </si>
+  <si>
+    <t>Escapar</t>
+  </si>
+  <si>
+    <t>Escape</t>
+  </si>
+  <si>
+    <t>YouWonTriesModal</t>
+  </si>
+  <si>
+    <t>YouWonModal_Title</t>
+  </si>
+  <si>
+    <t>¡Ganaste!</t>
+  </si>
+  <si>
+    <t>You Won!</t>
+  </si>
+  <si>
+    <t>Descipción de página</t>
+  </si>
+  <si>
+    <t>Debe ser una felicitación</t>
+  </si>
+  <si>
+    <t>SecretCodeLbl</t>
+  </si>
+  <si>
+    <t>Lable</t>
+  </si>
+  <si>
+    <t>YouWonTriesModal_SecretCode</t>
+  </si>
+  <si>
+    <t>El Código Secreto era:</t>
+  </si>
+  <si>
+    <t>The Secret Code was:</t>
+  </si>
+  <si>
+    <t>ContinueBtn</t>
+  </si>
+  <si>
+    <t>UI_Continue</t>
+  </si>
+  <si>
+    <t>Continuar</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
+    <t>Cierre de modal</t>
+  </si>
+  <si>
+    <t>YouWonTimeTrialModal</t>
+  </si>
+  <si>
+    <t>DecipheringTimeLbl</t>
+  </si>
+  <si>
+    <t>YouWonTimeTrialModal_DecipheringTime</t>
+  </si>
+  <si>
+    <t>Descifraste el código secreto en:</t>
+  </si>
+  <si>
+    <t>Yo deciphered the secret code in:</t>
+  </si>
+  <si>
+    <t>YouWonTimeTrialModal_Seconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Segundos!</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Seconds!</t>
+  </si>
+  <si>
+    <t>GameOverModal</t>
+  </si>
+  <si>
+    <t>GameOverTriesModal_Title</t>
+  </si>
+  <si>
+    <t>¡Te quedaste sin intentos!</t>
+  </si>
+  <si>
+    <t>You ran out of tries!</t>
+  </si>
+  <si>
+    <t>GameOverTimeTrialModal_Title</t>
+  </si>
+  <si>
+    <t>¡Se acabó el Tiempo!</t>
+  </si>
+  <si>
+    <t>Time's Up!</t>
+  </si>
+  <si>
+    <t>GameOverLbl</t>
+  </si>
+  <si>
+    <t>GameOverModal_GameOver</t>
+  </si>
+  <si>
+    <t>Fin del Juego</t>
+  </si>
+  <si>
+    <t>Game Over</t>
+  </si>
+  <si>
+    <t>NewPasswordModal</t>
+  </si>
+  <si>
+    <t>NewPasswordModal_Title</t>
+  </si>
+  <si>
+    <t>Escribe tu nueva contraseña</t>
+  </si>
+  <si>
+    <t>Type your new password</t>
+  </si>
+  <si>
+    <t>FriendsModal</t>
+  </si>
+  <si>
+    <t>FriendsModal_Title</t>
+  </si>
+  <si>
+    <t>FriendRequestsBtn</t>
+  </si>
+  <si>
+    <t>FriendRequestsModal_Title</t>
+  </si>
+  <si>
+    <t>Solicitudes de amistad</t>
+  </si>
+  <si>
+    <t>Friend Requests</t>
+  </si>
+  <si>
+    <t>CloseBtn</t>
+  </si>
+  <si>
+    <t>UI_Close</t>
+  </si>
+  <si>
+    <t>Cerrar</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>Cierre de Modal</t>
+  </si>
+  <si>
+    <t>FriendRequestsModal</t>
+  </si>
+  <si>
+    <t>Solicitudes de Amistad</t>
+  </si>
+  <si>
+    <t>NewFriendTxt</t>
+  </si>
+  <si>
+    <t>FriendRequestsModal_AddFriendText</t>
+  </si>
+  <si>
+    <t>Agregar un nuevo amigo</t>
+  </si>
+  <si>
+    <t>Add a new friend</t>
+  </si>
+  <si>
+    <t>SuccessNotificationModal</t>
+  </si>
+  <si>
+    <t>SuccessNotification_Title</t>
+  </si>
+  <si>
+    <t>¡Éxito!</t>
+  </si>
+  <si>
+    <t>Success!</t>
+  </si>
+  <si>
+    <t>NotificationMessageTxt</t>
+  </si>
+  <si>
+    <t>TextBlock</t>
+  </si>
+  <si>
+    <t>SuccessNotification_Register</t>
+  </si>
+  <si>
+    <t>¡Tu cuenta fue registrada con éxito! Se envió un correo de verificación a tu correo</t>
+  </si>
+  <si>
+    <t>Your account was successfully registered! A verification code was sent to your email</t>
+  </si>
+  <si>
+    <t>Aviso</t>
+  </si>
+  <si>
+    <t>NotificationModal_DefaultMessage</t>
+  </si>
+  <si>
+    <t>Si ves este mensaje, algo salió mal. Contacta a soporte técnico.</t>
+  </si>
+  <si>
+    <t>If you see this message, something went wrong. Contact tech support.</t>
+  </si>
+  <si>
+    <t>SuccessNotification_FriendRequestSent</t>
+  </si>
+  <si>
+    <t>¡La solicitud de amistad fue enviada con éxito!</t>
+  </si>
+  <si>
+    <t>The friend request was successfully sent!</t>
+  </si>
+  <si>
+    <t>ErrorNotificationModal</t>
+  </si>
+  <si>
+    <t>ErrorNotification_Title</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>ErrorNotification_InvalidInput</t>
+  </si>
+  <si>
+    <t>Uno o más campos que ingresaste son inválidos, revisa por favor que no haya campos vacíos, que el formato sea correcto y que la contraseña tenga mínimo 8 caracteres, una mayúscula, una minúscula y un número</t>
+  </si>
+  <si>
+    <t>One or more fields you entered are invalid, please check that there are no empty fields, that the format is correct and that the password has a minimum of 8 characters, an uppercase letter, a lowercase letter and a number</t>
+  </si>
+  <si>
+    <t>ErrorNotification_WhiteInput</t>
+  </si>
+  <si>
+    <t>Uno o más campos que ingresaste están campos vacíos, no debe haber ningún campo de registro vacío.</t>
+  </si>
+  <si>
+    <t>One or more fields you entered are empty fields, there should not be any empty record fields.</t>
+  </si>
+  <si>
+    <t>ErrorNotification_InvalidPassword</t>
+  </si>
+  <si>
+    <t>La contraseña debe tener mínimo 8 caracteres, una mayúscula, una minúscula y un número</t>
+  </si>
+  <si>
+    <t>The password must be at least 8 characters, one uppercase, one lowercase and one number</t>
+  </si>
+  <si>
+    <t>ErrorNotification_InvalidEmail</t>
+  </si>
+  <si>
+    <t>La dirección de correo debe tener un formato válido. Revisa que tenga solo un '@', y que tenga una extensión válida como .com</t>
+  </si>
+  <si>
+    <t>The email address must be in a valid format. Check that it has only one '@', and that it has a valid extension like .com</t>
+  </si>
+  <si>
+    <t>ErrorNotification_InvalidCredentials</t>
+  </si>
+  <si>
+    <t>Las credenciales ingresadas son incorrectas</t>
+  </si>
+  <si>
+    <t>The credentials entered are incorrect</t>
+  </si>
+  <si>
+    <t>ErrorNotification_UsernameTaken</t>
+  </si>
+  <si>
+    <t>El nombre de usuario ingresado ya está en uso, prueba uno distinto por favor</t>
+  </si>
+  <si>
+    <t>The username entered is taken, please try a different one</t>
+  </si>
+  <si>
+    <t>ErrorNotification_EmailTaken</t>
+  </si>
+  <si>
+    <t>La dirección de correo electrónico ingresada ya está en uso, prueba una distinta por favor</t>
+  </si>
+  <si>
+    <t>The email entered is taken, please try a different one</t>
+  </si>
+  <si>
+    <t>ErrorNotification_WrongCode</t>
+  </si>
+  <si>
+    <t>El código de verificación ingresado es incorrecto, intenta de nuevo.</t>
+  </si>
+  <si>
+    <t>The verification code you typed is wrong, try again.</t>
+  </si>
+  <si>
+    <t>ErrorNotification_ErrorSendingFriendRequest</t>
+  </si>
+  <si>
+    <t>Hubo un error al enviar la solicitud de amistad. Intenta de nuevo más tarde</t>
+  </si>
+  <si>
+    <t>There was an error while sending your friend request. Try later</t>
+  </si>
+  <si>
+    <t>ErrorNotification_FriendRequestPending</t>
+  </si>
+  <si>
+    <t>La solicitud de amistad enviada a este jugador está en espera de ser aceptada</t>
+  </si>
+  <si>
+    <t>The friend request sent to this player is waiting to be accepted</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -206,6 +1031,10 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -221,7 +1050,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -230,6 +1059,15 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,12 +1286,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="15.88"/>
+    <col customWidth="1" min="1" max="1" width="20.13"/>
+    <col customWidth="1" min="2" max="2" width="18.38"/>
     <col customWidth="1" min="3" max="3" width="14.63"/>
-    <col customWidth="1" min="4" max="4" width="23.25"/>
+    <col customWidth="1" min="4" max="4" width="30.25"/>
     <col customWidth="1" min="5" max="5" width="18.5"/>
     <col customWidth="1" min="6" max="6" width="19.88"/>
-    <col customWidth="1" min="8" max="8" width="15.0"/>
+    <col customWidth="1" min="8" max="8" width="23.5"/>
     <col customWidth="1" min="9" max="9" width="27.0"/>
   </cols>
   <sheetData>
@@ -538,7 +1377,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>17</v>
@@ -549,28 +1388,28 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -578,25 +1417,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -604,28 +1443,28 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -633,28 +1472,28 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -662,77 +1501,48 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -746,115 +1556,2641 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="D49" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I74" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>36</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
